--- a/wildlife/reports/United-Kingdom/composition/Abingdon/Butterflies/composition.xlsx
+++ b/wildlife/reports/United-Kingdom/composition/Abingdon/Butterflies/composition.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
